--- a/cartographie/A_FAIRE.xlsx
+++ b/cartographie/A_FAIRE.xlsx
@@ -543,7 +543,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C'est la seule tache dont depend une mesure qu'on ne peut pas faire sans toi.</t>
+          <t>C'est la seule tache dont dependent DEUX mesures qu'on ne peut pas faire sans toi : ce que vaut une de nos deux methodes de detection, et quelle part des collaborations le projet voit.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>218 noms tires des videos publiees par les lobbies EUX-MEMES. Une seule question : createur, ou nom de serie ? Tes reponses mesureront la voie « motif dans le titre », 176 noms dont on ignore ce qu'elle vaut. Si elle ne donne que des series, on l'abandonne.</t>
+          <t>218 noms tires des videos publiees par les lobbies EUX-MEMES. DEUX questions, et elles debloquent deux mesures independantes. (1) Createur ou nom de serie ? — cela mesure la voie « motif dans le titre », 176 noms dont on ignore ce qu'elle vaut. (2) Quel TYPE de personne ? — cela tranche la question de la couverture du projet : nos deux methodes trouvent 36 et 42 createurs et n'ont qu'UN nom en commun. Soit on rate enormement, soit les deux methodes cherchent des gens differents. Si ces noms sont surtout des chefs et des eleveurs, c'est la seconde explication. Voir JOURNAL 62.</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -996,15 +996,32 @@
     <row r="5" ht="76" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>METHODOLOGIE 9.2 prescrit une mesure impossible. La reecrire ?</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Oui — remplacer le tirage aleatoire par la capture-recapture.</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>La section demande de tirer des createurs au hasard et de les annoter exhaustivement, pour savoir ce que le projet rate. MESURE du 27/08 : 1,35 % des chaines portent une preuve forte, donc il faudrait en annoter 739 A LA MAIN pour en obtenir dix, soit 28 % du registre. Et 83 % pour en obtenir trente. Ce n'est pas un manque de temps, c'est arithmetiquement impossible. La voie de rechange existe deja en section 9.3 — et les chaines des lobbies sont la seconde source independante qui manquait. Voir JOURNAL 62.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>Qui publie le registre, et sous quel nom ?</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Question ouverte, sans urgence technique.</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Elle devient urgente le jour ou le premier nom sort. Rien ne se publie sans verification humaine — METHODOLOGIE section 9.</t>
         </is>
@@ -1021,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1117,32 +1134,66 @@
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Moisson TikTok</t>
+          <t>Le tirage aleatoire de METHODOLOGIE 9.2</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>BLOQUEE JUSQU'A DEMAIN</t>
+          <t>MESURE IMPOSSIBLE</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Quota journalier epuise a 5 mois sur 47. Reprend toute seule, les 42 mois restants ne sont pas marques faits.</t>
+          <t>Il faudrait annoter 739 chaines a la main pour en obtenir dix qui portent une preuve. La prescription doit etre revue — c'est une decision de methode, elle est dans l'onglet DECISIONS.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Les six regles de detection</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>REMESUREES</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>B, C, D et F font toutes 85 % de precision. B a le meilleur rappel et n'a aucune liste ecrite a la main. Recommandation dans l'onglet DECISIONS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Moisson TikTok</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>BLOQUEE JUSQU'A DEMAIN</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Quota journalier epuise a 5 mois sur 47. Reprend toute seule, les 42 mois restants ne sont pas marques faits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>BLOQUE SUR TOI</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Rien ne peut avancer sans le jeton Meta — tache 3.</t>
         </is>

--- a/cartographie/A_FAIRE.xlsx
+++ b/cartographie/A_FAIRE.xlsx
@@ -707,12 +707,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Verifier les createurs LAIT'FLIX</t>
+          <t>Verifier les createurs nommes sur les sites des lobbies</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>cartographie/LAITFLIX_A_VERIFIER.xlsx</t>
+          <t>cartographie/CREATEURS_SUR_LES_SITES.xlsx</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>107 videos en 12 series sur produits-laitiers.com, que TU as reperees. Neuf des douze series sont ABSENTES de la chaine YouTube du CNIEL : moissonner la chaine officielle d'un lobby ne suffit donc pas. La liste vient d'une lecture automatique de la page et doit etre verifiee.</t>
+          <t>Quatre sources relevees le 28/08 : le catalogue LAIT'FLIX du CNIEL (107 videos, 12 series — la page que TU avais signalee), la-viande.fr pour INTERBEV (Cyril Lignac, Loic Ballet), et les publicites Facebook payees par le CIFOG et ANVOL. Neuf des douze series LAIT'FLIX sont ABSENTES de la chaine YouTube du CNIEL : moissonner la chaine officielle d'un lobby ne suffit pas. Liste issue d'une lecture automatique, a verifier.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -1140,17 +1140,17 @@
     <row r="5" ht="84" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>LAITFLIX_A_VERIFIER.xlsx</t>
+          <t>CREATEURS_SUR_LES_SITES.xlsx</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Createurs des series LAIT'FLIX</t>
+          <t>Createurs nommes sur les sites et dans les pubs des lobbies</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>60 lignes</t>
+          <t>70 lignes</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>60 restantes</t>
+          <t>70 restantes</t>
         </is>
       </c>
     </row>

--- a/cartographie/A_FAIRE.xlsx
+++ b/cartographie/A_FAIRE.xlsx
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OU EN EST LE PROJET — 28/08/2026</t>
+          <t>OU EN EST LE PROJET — 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -1069,17 +1069,17 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>218 lignes</t>
+          <t>228 lignes</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>36 jugees</t>
+          <t>35 jugees</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>182 restantes</t>
+          <t>193 restantes</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1297,20 +1297,38 @@
     <row r="6" ht="84" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Faut-il couvrir Twitch ?</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Oui, mais en dernier — apres les classeurs a juger.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MESURE du 29/08, qui tranche une question ouverte depuis le 24. On croyait Twitch couvert indirectement, parce que l'INAPORC ecrit sur son site que les best-of de ses lives migrent vers YouTube. Verification sur le catalogue COMPLET de Lebouseuh (1 773 videos) et 300 de Gastronogeek : ZERO mention d'INAPORC ou du Porc Francais. Les best-of n'y sont pas. Twitch est donc un angle mort reel. Ce que ca coute : l'API Twitch est gratuite et expose les CLIPS, qui sont permanents. Les VOD expirent en 14 a 60 jours — on verrait le present, jamais l'archive. Il faudrait creer un compte developpeur Twitch, comme pour Meta. JOURNAL 70.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="84" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Qui publie le registre, et sous quel nom ?</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Sans urgence — tu as deja repondu et j'ai note.</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Ta reponse du 27/08 : « On est a l'etape de creer une methode de scrapping robuste et resiliente. Le but est de creer un dataset solide [...] Une fois qu'on aura ce dataset, on reflechira a la forme du site. » C'est enregistre. La question ne se rouvre qu'au moment de publier.</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>On est a l'etape de creer une methode de scrapping robuste et resiliente. Le but est de creer un dataset solide avec nom des influenceurs, lobby/vitrine/marque qui remunere, date de la collaboration, eventuellement le montant, la forme (type et nombre de contenus), les plateformes. Une fois ce dataset obtenu et une methode pour le mettre a jour, on reflechira a la forme du site, a l'extension de navigateur, au bouton de signalement, et a quoi faire de ces donnees.</t>
         </is>

--- a/cartographie/A_FAIRE.xlsx
+++ b/cartographie/A_FAIRE.xlsx
@@ -674,22 +674,22 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Trancher CREATEURS_DANS_LES_ANNONCES.xlsx</t>
+          <t>Trancher ANNONCES_A_JUGER.xlsx</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>cartographie/CREATEURS_DANS_LES_ANNONCES.xlsx</t>
+          <t>cartographie/ANNONCES_A_JUGER.xlsx</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>20 min pour les 80 premieres lignes</t>
+          <t>25 min pour les 90 lignes</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>617 createurs nommes dans des PUBLICITES PAYEES par la filiere, sorties de la Meta Ad Library le 27/08. C'est la preuve la plus forte du projet : l'annonceur a paye pour diffuser. Trois voies de detection a mesurer.</t>
+          <t>90 createurs, 30 par methode de detection — echantillon EQUILIBRE, pas proportionnel : on veut mesurer chaque methode, pas refleter son volume. Ce canal fournit la plus grosse part du jeu de donnees et c'est le SEUL dont la precision n'a jamais ete mesuree. Corrige depuis ta lecture du 29/08 : les liens pointent vers la bibliotheque publicitaire PUBLIQUE de Meta (plus de jeton, plus de liens morts), et les pseudos de marque comme @regilaitfr sont ecartes.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="3" ht="84" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>CREATEURS_DANS_LES_ANNONCES.xlsx</t>
+          <t>ANNONCES_A_JUGER.xlsx</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>617 lignes</t>
+          <t>90 lignes</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>617 restantes</t>
+          <t>90 restantes</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>0 jugees</t>
+          <t>9 jugees</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>9 restantes</t>
+          <t>0 restantes</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>0 jugees</t>
+          <t>68 jugees</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>70 restantes</t>
+          <t>2 restantes</t>
         </is>
       </c>
     </row>

--- a/cartographie/A_FAIRE.xlsx
+++ b/cartographie/A_FAIRE.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -669,27 +669,27 @@
     <row r="2" ht="84" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2 — le plus neuf</t>
+          <t>0 — AVANT TOUT LE RESTE</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Trancher ANNONCES_A_JUGER.xlsx</t>
+          <t>Construire toi-meme un jeu de donnees de depart</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>cartographie/ANNONCES_A_JUGER.xlsx</t>
+          <t>A la main, dans le format que tu veux</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>25 min pour les 90 lignes</t>
+          <t>le temps qu'il faut</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>90 createurs, 30 par methode de detection — echantillon EQUILIBRE, pas proportionnel : on veut mesurer chaque methode, pas refleter son volume. Ce canal fournit la plus grosse part du jeu de donnees et c'est le SEUL dont la precision n'a jamais ete mesuree. Corrige depuis ta lecture du 29/08 : les liens pointent vers la bibliotheque publicitaire PUBLIQUE de Meta (plus de jeton, plus de liens morts), et les pseudos de marque comme @regilaitfr sont ecartes.</t>
+          <t>Tu l'as decide le 29/08 : « je vais faire le travail moi-meme, avec mon bon vieux cerveau d'humain, et expliquer mieux ce que je peux attendre de toi apres ». C'est la bonne decision — la semaine a montre que je construisais des outils sans modele de donnees, et que je te faisais valider des sorties brutes plutot que des entites. Rien ne sera reconstruit avant d'avoir vu ton fichier.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -697,32 +697,36 @@
           <t>pas encore</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Prevu pour le 30/08.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="84" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2 — le plus neuf</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Verifier les createurs nommes sur les sites des lobbies</t>
+          <t>Trancher ANNONCES_A_JUGER.xlsx</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>cartographie/CREATEURS_SUR_LES_SITES.xlsx</t>
+          <t>cartographie/ANNONCES_A_JUGER.xlsx</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>25 min pour les 90 lignes</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Quatre sources relevees le 28/08 : le catalogue LAIT'FLIX du CNIEL (107 videos, 12 series — la page que TU avais signalee), la-viande.fr pour INTERBEV (Cyril Lignac, Loic Ballet), et les publicites Facebook payees par le CIFOG et ANVOL. Neuf des douze series LAIT'FLIX sont ABSENTES de la chaine YouTube du CNIEL : moissonner la chaine officielle d'un lobby ne suffit pas. Liste issue d'une lecture automatique, a verifier.</t>
+          <t>90 createurs, 30 par methode de detection — echantillon EQUILIBRE, pas proportionnel : on veut mesurer chaque methode, pas refleter son volume. Ce canal fournit la plus grosse part du jeu de donnees et c'est le SEUL dont la precision n'a jamais ete mesuree. Corrige depuis ta lecture du 29/08 : les liens pointent vers la bibliotheque publicitaire PUBLIQUE de Meta (plus de jeton, plus de liens morts), et les pseudos de marque comme @regilaitfr sont ecartes.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -730,36 +734,32 @@
           <t>pas encore</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>produits-laitiers.com/laitflix/divertissement est une mine d'or. Je peux lister les creatures des series si tu n'y arrives pas.</t>
-        </is>
-      </c>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="84" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>4 — a refaire chaque fois</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Regenerer le jeton Meta</t>
+          <t>Verifier les createurs nommes sur les sites des lobbies</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>developers.facebook.com/tools/explorer — app, User Token, ads_read, Generate. Coller dans SECRETS.txt</t>
+          <t>cartographie/CREATEURS_SUR_LES_SITES.xlsx</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Le jeton expire en 1 a 2 heures. Sans lui, aucune moisson Instagram. Le chemin est maintenant connu et teste.</t>
+          <t>Quatre sources relevees le 28/08 : le catalogue LAIT'FLIX du CNIEL (107 videos, 12 series — la page que TU avais signalee), la-viande.fr pour INTERBEV (Cyril Lignac, Loic Ballet), et les publicites Facebook payees par le CIFOG et ANVOL. Neuf des douze series LAIT'FLIX sont ABSENTES de la chaine YouTube du CNIEL : moissonner la chaine officielle d'un lobby ne suffit pas. Liste issue d'une lecture automatique, a verifier.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -769,24 +769,24 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Le chemin est etabli : ajouter le use case Marketing API a l'app fait apparaitre ads_read. C'est TOI qui l'as trouve le 27/08. A refaire a chaque session Meta.</t>
+          <t>produits-laitiers.com/laitflix/divertissement est une mine d'or. Je peux lister les creatures des series si tu n'y arrives pas.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="84" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 — a refaire chaque fois</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Juger A_VERIFIER_4.xlsx</t>
+          <t>Regenerer le jeton Meta</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>cartographie/A_VERIFIER_4.xlsx</t>
+          <t>developers.facebook.com/tools/explorer — app, User Token, ads_read, Generate. Coller dans SECRETS.txt</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>9 nouveaux candidats seulement — tes 78 jugements du 27/08 ont ete integres. Le jeu de reference atteint 382 videos jugees.</t>
+          <t>Le jeton expire en 1 a 2 heures. Sans lui, aucune moisson Instagram. Le chemin est maintenant connu et teste.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Tes 78 jugements du 27/08 portaient sur A_VERIFIER_3, deja integres. Ces 9-ci sont nouveaux.</t>
+          <t>Le chemin est etabli : ajouter le use case Marketing API a l'app fait apparaitre ads_read. C'est TOI qui l'as trouve le 27/08. A refaire a chaque session Meta.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="84" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>6 — quand rien ne tourne</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Sortir le projet de OneDrive et retirer le « &amp; » du nom</t>
+          <t>Juger A_VERIFIER_4.xlsx</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Couper-coller le dossier vers C:\Users\Vincent\veille-filiere</t>
+          <t>cartographie/A_VERIFIER_4.xlsx</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Deux problemes d'un geste. OneDrive : un verrou de synchronisation a interrompu une moisson. Le « &amp; » : cmd.exe le lit comme un separateur de commandes, il a fait echouer la tache planifiee au premier essai. APRES le deplacement il faut recreer la tache planifiee — dis-le moi, c'est une commande.</t>
+          <t>9 nouveaux candidats seulement — tes 78 jugements du 27/08 ont ete integres. Le jeu de reference atteint 382 videos jugees.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -841,32 +841,36 @@
           <t>pas encore</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Tes 78 jugements du 27/08 portaient sur A_VERIFIER_3, deja integres. Ces 9-ci sont nouveaux.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="84" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6 — quand rien ne tourne</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Relever les abonnements des vitrines sur TIKTOK et YOUTUBE</t>
+          <t>Sortir le projet de OneDrive et retirer le « &amp; » du nom</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>@lesproduitslaitiers, @la_viande_fr, @naturellementflexitariens, @volaillefrancaise, @lefoiegras — sur ces deux plateformes-la</t>
+          <t>Couper-coller le dossier vers C:\Users\Vincent\veille-filiere</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Les abonnements different d'une plateforme a l'autre. Meme rendement attendu que la semence Instagram.</t>
+          <t>Deux problemes d'un geste. OneDrive : un verrou de synchronisation a interrompu une moisson. Le « &amp; » : cmd.exe le lit comme un separateur de commandes, il a fait echouer la tache planifiee au premier essai. APRES le deplacement il faut recreer la tache planifiee — dis-le moi, c'est une commande.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -874,81 +878,114 @@
           <t>pas encore</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Tu veux que je t'envoie ca dans le CLI aussi et tu ranges toi ? — OUI, en vrac, l'outil qui lit les copier-coller existe.</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="84" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>9 — en cours</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Demander a L214 et Foodwatch si le registre existe deja</t>
+          <t>Relever les abonnements des vitrines sur TIKTOK et YOUTUBE</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Un courriel — ou via la responsable de Paye Ton Influence</t>
+          <t>@lesproduitslaitiers, @la_viande_fr, @naturellementflexitariens, @volaillefrancaise, @lefoiegras — sur ces deux plateformes-la</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Si quelqu'un l'a deja construit, autant le savoir. Tu as un appel prevu avec Paye Ton Influence : la question peut passer par la.</t>
+          <t>Les abonnements different d'une plateforme a l'autre. Meme rendement attendu que la semence Instagram.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>en cours</t>
+          <t>pas encore</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Je demanderai a la responsable de Paye Ton Influence si c'est une bonne idee d'abord. Appel prevu cette semaine.</t>
+          <t>Tu veux que je t'envoie ca dans le CLI aussi et tu ranges toi ? — OUI, en vrac, l'outil qui lit les copier-coller existe.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="84" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>9 — en cours</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Demander a L214 et Foodwatch si le registre existe deja</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Un courriel — ou via la responsable de Paye Ton Influence</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Si quelqu'un l'a deja construit, autant le savoir. Tu as un appel prevu avec Paye Ton Influence : la question peut passer par la.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>en cours</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Je demanderai a la responsable de Paye Ton Influence si c'est une bonne idee d'abord. Appel prevu cette semaine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="84" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
           <t>10 — en cours</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Demander a l'ARPP les donnees brutes de son Observatoire</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Un courriel</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Source officielle sur les communications commerciales des influenceurs. Ta reserve est notee : l'ARPP est un organisme d'autoregulation de la publicite, pas un regulateur public. Un refus est documentable.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>en cours</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Pas sur de l'aspect officiel, ca ressemble a un potentiel meta-lobby. Je demande l'avis a un collegue.</t>
         </is>
@@ -956,7 +993,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=listes!$A$1:$A$5</formula1>
     </dataValidation>
   </dataValidations>
